--- a/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -88,12 +88,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFCD5C5C"/>
+        <x:fgColor rgb="FFA9A9A9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA9A9A9"/>
+        <x:fgColor rgb="FFCD5C5C"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -169,7 +169,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="46" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -196,7 +196,7 @@
     <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -243,7 +243,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -279,7 +279,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -616,24 +616,24 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -701,10 +701,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="7" t="s"/>
+      <x:c r="A1" s="2" t="s"/>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="3" t="s"/>
+      <x:c r="A2" s="7" t="s"/>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="1" t="s">
@@ -727,7 +727,7 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="2" t="s">
+      <x:c r="A7" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -764,7 +764,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -784,10 +784,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -818,36 +818,36 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
+      <x:c r="A2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="A3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
         <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -924,7 +924,7 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="2" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -934,7 +934,7 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" s="7" t="s"/>
@@ -967,7 +967,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -987,10 +987,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1011,24 +1011,24 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -1147,24 +1147,24 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
+      <x:c r="A5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="s">
+      <x:c r="A6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1213,24 +1213,24 @@
       <x:c r="C1" s="6" t="s"/>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="A2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1301,13 +1301,13 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
+      <x:c r="A1" s="5" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
+      <x:c r="A2" s="1" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
@@ -1321,7 +1321,7 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="2" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -1331,10 +1331,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1369,22 +1369,22 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="2" t="s">
+      <x:c r="A4" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="1" t="s">
-        <x:v>3</x:v>
+      <x:c r="A5" s="5" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
+      <x:c r="A6" s="1" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" s="7" t="s"/>
@@ -1441,55 +1441,55 @@
       <x:c r="C3" s="5" t="s"/>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s"/>
+      <x:c r="A4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="A5" s="7" t="s"/>
+      <x:c r="B5" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>5</x:v>
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="s">
-        <x:v>6</x:v>
+      <x:c r="A7" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A8" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s"/>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="8" t="s">
@@ -1556,42 +1556,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="s">
+      <x:c r="A1" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
-      <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="5" t="s">
-        <x:v>3</x:v>
+      <x:c r="A2" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
-      <x:c r="A3" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="A3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="A4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
-      <x:c r="A5" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
+      <x:c r="A5" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -1599,8 +1599,8 @@
       <x:c r="A6" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>5</x:v>
+      <x:c r="B6" s="6" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1663,7 +1663,7 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" s="7" t="s"/>
@@ -1701,7 +1701,7 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="2" t="n">
+      <x:c r="A4" s="3" t="n">
         <x:v>4.3</x:v>
       </x:c>
     </x:row>
@@ -1716,10 +1716,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1769,7 +1769,7 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" s="7" t="s"/>
@@ -1822,10 +1822,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1865,24 +1865,24 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="A4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
